--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-04.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-04.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583998407262</v>
+        <v>5583987357458</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Maria do Socorro Dias de Lacerda</t>
+          <t>Michelle da Silva Nogueira</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583998855268</v>
+        <v>5583986190187</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Divaneide</t>
+          <t>Wictor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Divaneide de Mendonca Chaves</t>
+          <t>Wictor Abner de Oliveira Jácome</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583994197227</v>
+        <v>5583998407262</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pedro Henrique Ribeiro Paiva Gomes</t>
+          <t>Maria do Socorro Dias de Lacerda</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583986256603</v>
+        <v>5583998855268</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mayene</t>
+          <t>Divaneide</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mayene de Lima</t>
+          <t>Divaneide de Mendonca Chaves</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583991846168</v>
+        <v>5583994197227</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Maria da Conceicao Rodrigues</t>
+          <t>Pedro Henrique Ribeiro Paiva Gomes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583988662140</v>
+        <v>5583986256603</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Mayene</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Antonio Marcos de Melo</t>
+          <t>Mayene de Lima</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583982303353</v>
+        <v>5583991846168</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ricardo</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ricardo de Oliveira Camilo</t>
+          <t>Maria da Conceicao Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583981871099</v>
+        <v>5583988662140</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Samara Matias Batista</t>
+          <t>Antonio Marcos de Melo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583988331420</v>
+        <v>5583982303353</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Odaci</t>
+          <t>Ricardo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Odaci de Lima Carneiro Junior</t>
+          <t>Ricardo de Oliveira Camilo</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583988958092</v>
+        <v>5583981871099</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eduardo Soares dos Santos</t>
+          <t>Samara Matias Batista</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583991226532</v>
+        <v>5583988331420</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Humberto</t>
+          <t>Odaci</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Humberto</t>
+          <t>Odaci de Lima Carneiro Junior</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583993762649</v>
+        <v>5583988958092</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bruno</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Eduardo Soares dos Santos</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583988845910</v>
+        <v>5583991226532</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Betania</t>
+          <t>Humberto</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Betania Alves do Nascimento</t>
+          <t>Humberto</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583987316873</v>
+        <v>5583993762649</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Bruno</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Marcos Gomes de Andrade</t>
+          <t>Bruno Henrique</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583988700893</v>
+        <v>5583988845910</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jailma</t>
+          <t>Betania</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jailma de Andrade dos Santos Borges</t>
+          <t>Betania Alves do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583998399066</v>
+        <v>5583987316873</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Flavia</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Flavia Guedes de Barros</t>
+          <t>Marcos Gomes de Andrade</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583986424582</v>
+        <v>5583988700893</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Jailma</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pedro Miguel de Araujo</t>
+          <t>Jailma de Andrade dos Santos Borges</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583987140943</v>
+        <v>5583998399066</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Flavia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ana Paula Gomes da Silva Lirnino</t>
+          <t>Flavia Guedes de Barros</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583988891939</v>
+        <v>5583986424582</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Luiza</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Luiza Paulino Romualdo</t>
+          <t>Pedro Miguel de Araujo</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583988402697</v>
+        <v>5583987140943</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hailson</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hailson da Silva Fernandes</t>
+          <t>Ana Paula Gomes da Silva Lirnino</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583981157263</v>
+        <v>5583988891939</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Luiza</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yasmin Brito de Lemos</t>
+          <t>Luiza Paulino Romualdo</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583999991808</v>
+        <v>5583988402697</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bruno</t>
+          <t>Hailson</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bruno Ferreira de Souza Queiroz</t>
+          <t>Hailson da Silva Fernandes</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583996085893</v>
+        <v>5583981157263</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fernando da Conceicao da Silva</t>
+          <t>Yasmin Brito de Lemos</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583999390392</v>
+        <v>5583999991808</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Davi</t>
+          <t>Bruno</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Davi Costa de Santana</t>
+          <t>Bruno Ferreira de Souza Queiroz</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583991397574</v>
+        <v>5583996085893</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Natali</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Natali de Oliveira Pontes</t>
+          <t>Fernando da Conceicao da Silva</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583987028638</v>
+        <v>5583999390392</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adslandson</t>
+          <t>Davi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Adslandson de Melo Gomes Peixoto</t>
+          <t>Davi Costa de Santana</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5583986180320</v>
+        <v>5583991397574</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tiago</t>
+          <t>Natali</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tiago Gonzaga do Nascimento</t>
+          <t>Natali de Oliveira Pontes</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583987016947</v>
+        <v>5583987028638</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jucelino</t>
+          <t>Adslandson</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jucelino da Silva</t>
+          <t>Adslandson de Melo Gomes Peixoto</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583996504861</v>
+        <v>5583986180320</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nubia</t>
+          <t>Tiago</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nubia da Costa Almeida</t>
+          <t>Tiago Gonzaga do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5583998924365</v>
+        <v>5583987016947</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eriosvaldo</t>
+          <t>Jucelino</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eriosvaldo Goncalves da Silva</t>
+          <t>Jucelino da Silva</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583988727870</v>
+        <v>5583996504861</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rosana</t>
+          <t>Nubia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rosana Gomes de Siqueira</t>
+          <t>Nubia da Costa Almeida</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5521996379359</v>
+        <v>5583998924365</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jozilda</t>
+          <t>Eriosvaldo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jozilda Henrique Oliveira</t>
+          <t>Eriosvaldo Goncalves da Silva</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5581983625256</v>
+        <v>5583988727870</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Construtora</t>
+          <t>Rosana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Construtora Lamm</t>
+          <t>Rosana Gomes de Siqueira</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583998892606</v>
+        <v>5521996379359</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Milena</t>
+          <t>Jozilda</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Milena Barbosa da Silva</t>
+          <t>Jozilda Henrique Oliveira</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583987819509</v>
+        <v>5581983625256</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jordanna</t>
+          <t>Construtora</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordanna da Silva Serafim</t>
+          <t>Construtora Lamm</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583987468742</v>
+        <v>5583998892606</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Renison</t>
+          <t>Milena</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Renison Guedes Evangelista</t>
+          <t>Milena Barbosa da Silva</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583988370705</v>
+        <v>5583987819509</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dirceu</t>
+          <t>Jordanna</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dirceu Henrique Gomes da Silva</t>
+          <t>Jordanna da Silva Serafim</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583988915710</v>
+        <v>5583987468742</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Renison</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ana Maria Ferreira</t>
+          <t>Renison Guedes Evangelista</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5581997880195</v>
+        <v>5583988370705</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pmi</t>
+          <t>Dirceu</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pmi</t>
+          <t>Dirceu Henrique Gomes da Silva</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583987623366</v>
+        <v>5583988915710</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Melquizedeque</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Melquizedeque dos Santos Cunha</t>
+          <t>Ana Maria Ferreira</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583998107775</v>
+        <v>5581997880195</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Pmi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jose Bruno de Arruda Ferreira</t>
+          <t>Pmi</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583986728173</v>
+        <v>5583987623366</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Marlene</t>
+          <t>Melquizedeque</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Marlene Tavares da Silva</t>
+          <t>Melquizedeque dos Santos Cunha</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583996856417</v>
+        <v>5583998107775</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Edmilson</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Edmilson do Nascimento Alves</t>
+          <t>Jose Bruno de Arruda Ferreira</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583986676627</v>
+        <v>5583986728173</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tatiane</t>
+          <t>Marlene</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tatiane de Oliveira Lima</t>
+          <t>Marlene Tavares da Silva</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5583994442453</v>
+        <v>5583996856417</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Alanna</t>
+          <t>Edmilson</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alanna Dantas Rodrigues</t>
+          <t>Edmilson do Nascimento Alves</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5583999577568</v>
+        <v>5583986676627</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Edivaldo</t>
+          <t>Tatiane</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Edivaldo Barbosa Tavares - Dorge</t>
+          <t>Tatiane de Oliveira Lima</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583981487398</v>
+        <v>5583994442453</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Alanna</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rafael da Silva</t>
+          <t>Alanna Dantas Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5583987185565</v>
+        <v>5583999577568</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Edivaldo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lucas Alves Diogo</t>
+          <t>Edivaldo Barbosa Tavares - Dorge</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583987180188</v>
+        <v>5583981487398</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lucelia</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lucelia dos Santos Costa</t>
+          <t>Rafael da Silva</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583996437484</v>
+        <v>5583987185565</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pedro Henrick Ribeiro de Melo</t>
+          <t>Lucas Alves Diogo</t>
         </is>
       </c>
     </row>
